--- a/scripts/sample_12_students.xlsx
+++ b/scripts/sample_12_students.xlsx
@@ -1,47 +1,200 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Students" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Students" state="visible" r:id="rId4"/>
   </sheets>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="57">
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>designation</t>
+  </si>
+  <si>
+    <t>uniqueKey</t>
+  </si>
+  <si>
+    <t>class</t>
+  </si>
+  <si>
+    <t>rollNo</t>
+  </si>
+  <si>
+    <t>bloodGroup</t>
+  </si>
+  <si>
+    <t>Aarav Sharma</t>
+  </si>
+  <si>
+    <t>Student</t>
+  </si>
+  <si>
+    <t>SA-2024-001</t>
+  </si>
+  <si>
+    <t>Grade 10-A</t>
+  </si>
+  <si>
+    <t>001</t>
+  </si>
+  <si>
+    <t>O+</t>
+  </si>
+  <si>
+    <t>Priya Patel</t>
+  </si>
+  <si>
+    <t>SA-2024-002</t>
+  </si>
+  <si>
+    <t>002</t>
+  </si>
+  <si>
+    <t>A+</t>
+  </si>
+  <si>
+    <t>Rohan Mehta</t>
+  </si>
+  <si>
+    <t>SA-2024-003</t>
+  </si>
+  <si>
+    <t>Grade 10-B</t>
+  </si>
+  <si>
+    <t>003</t>
+  </si>
+  <si>
+    <t>B+</t>
+  </si>
+  <si>
+    <t>Ananya Singh</t>
+  </si>
+  <si>
+    <t>SA-2024-004</t>
+  </si>
+  <si>
+    <t>004</t>
+  </si>
+  <si>
+    <t>AB+</t>
+  </si>
+  <si>
+    <t>Karan Verma</t>
+  </si>
+  <si>
+    <t>SA-2024-005</t>
+  </si>
+  <si>
+    <t>Grade 11-A</t>
+  </si>
+  <si>
+    <t>005</t>
+  </si>
+  <si>
+    <t>O-</t>
+  </si>
+  <si>
+    <t>Diya Gupta</t>
+  </si>
+  <si>
+    <t>SA-2024-006</t>
+  </si>
+  <si>
+    <t>006</t>
+  </si>
+  <si>
+    <t>A-</t>
+  </si>
+  <si>
+    <t>Arjun Nair</t>
+  </si>
+  <si>
+    <t>SA-2024-007</t>
+  </si>
+  <si>
+    <t>Grade 11-B</t>
+  </si>
+  <si>
+    <t>007</t>
+  </si>
+  <si>
+    <t>B-</t>
+  </si>
+  <si>
+    <t>Shreya Iyer</t>
+  </si>
+  <si>
+    <t>SA-2024-008</t>
+  </si>
+  <si>
+    <t>008</t>
+  </si>
+  <si>
+    <t>AB-</t>
+  </si>
+  <si>
+    <t>Vikram Reddy</t>
+  </si>
+  <si>
+    <t>SA-2024-009</t>
+  </si>
+  <si>
+    <t>Grade 12-A</t>
+  </si>
+  <si>
+    <t>009</t>
+  </si>
+  <si>
+    <t>Meera Krishnan</t>
+  </si>
+  <si>
+    <t>SA-2024-010</t>
+  </si>
+  <si>
+    <t>010</t>
+  </si>
+  <si>
+    <t>Aditya Bose</t>
+  </si>
+  <si>
+    <t>SA-2024-011</t>
+  </si>
+  <si>
+    <t>Grade 12-B</t>
+  </si>
+  <si>
+    <t>011</t>
+  </si>
+  <si>
+    <t>Kavya Menon</t>
+  </si>
+  <si>
+    <t>SA-2024-012</t>
+  </si>
+  <si>
+    <t>012</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -65,13 +218,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,280 +557,279 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F13"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="25.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" customWidth="1"/>
-    <col min="3" max="3" width="15.83203125" customWidth="1"/>
-    <col min="4" max="4" width="15.83203125" customWidth="1"/>
-    <col min="5" max="5" width="10.83203125" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="4" width="15" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>name</v>
-      </c>
-      <c r="B1" t="str">
-        <v>designation</v>
-      </c>
-      <c r="C1" t="str">
-        <v>uniqueKey</v>
-      </c>
-      <c r="D1" t="str">
-        <v>class</v>
-      </c>
-      <c r="E1" t="str">
-        <v>rollNo</v>
-      </c>
-      <c r="F1" t="str">
-        <v>bloodGroup</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Aarav Sharma</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Student</v>
-      </c>
-      <c r="C2" t="str">
-        <v>SA-2024-001</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Grade 10-A</v>
-      </c>
-      <c r="E2" t="str">
-        <v>001</v>
-      </c>
-      <c r="F2" t="str">
-        <v>O+</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Priya Patel</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Student</v>
-      </c>
-      <c r="C3" t="str">
-        <v>SA-2024-002</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Grade 10-A</v>
-      </c>
-      <c r="E3" t="str">
-        <v>002</v>
-      </c>
-      <c r="F3" t="str">
-        <v>A+</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Rohan Mehta</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Student</v>
-      </c>
-      <c r="C4" t="str">
-        <v>SA-2024-003</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Grade 10-B</v>
-      </c>
-      <c r="E4" t="str">
-        <v>003</v>
-      </c>
-      <c r="F4" t="str">
-        <v>B+</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Ananya Singh</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Student</v>
-      </c>
-      <c r="C5" t="str">
-        <v>SA-2024-004</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Grade 10-B</v>
-      </c>
-      <c r="E5" t="str">
-        <v>004</v>
-      </c>
-      <c r="F5" t="str">
-        <v>AB+</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Karan Verma</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Student</v>
-      </c>
-      <c r="C6" t="str">
-        <v>SA-2024-005</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Grade 11-A</v>
-      </c>
-      <c r="E6" t="str">
-        <v>005</v>
-      </c>
-      <c r="F6" t="str">
-        <v>O-</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Diya Gupta</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Student</v>
-      </c>
-      <c r="C7" t="str">
-        <v>SA-2024-006</v>
-      </c>
-      <c r="D7" t="str">
-        <v>Grade 11-A</v>
-      </c>
-      <c r="E7" t="str">
-        <v>006</v>
-      </c>
-      <c r="F7" t="str">
-        <v>A-</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Arjun Nair</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Student</v>
-      </c>
-      <c r="C8" t="str">
-        <v>SA-2024-007</v>
-      </c>
-      <c r="D8" t="str">
-        <v>Grade 11-B</v>
-      </c>
-      <c r="E8" t="str">
-        <v>007</v>
-      </c>
-      <c r="F8" t="str">
-        <v>B-</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Shreya Iyer</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Student</v>
-      </c>
-      <c r="C9" t="str">
-        <v>SA-2024-008</v>
-      </c>
-      <c r="D9" t="str">
-        <v>Grade 11-B</v>
-      </c>
-      <c r="E9" t="str">
-        <v>008</v>
-      </c>
-      <c r="F9" t="str">
-        <v>AB-</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Vikram Reddy</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Student</v>
-      </c>
-      <c r="C10" t="str">
-        <v>SA-2024-009</v>
-      </c>
-      <c r="D10" t="str">
-        <v>Grade 12-A</v>
-      </c>
-      <c r="E10" t="str">
-        <v>009</v>
-      </c>
-      <c r="F10" t="str">
-        <v>O+</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Meera Krishnan</v>
-      </c>
-      <c r="B11" t="str">
-        <v>Student</v>
-      </c>
-      <c r="C11" t="str">
-        <v>SA-2024-010</v>
-      </c>
-      <c r="D11" t="str">
-        <v>Grade 12-A</v>
-      </c>
-      <c r="E11" t="str">
-        <v>010</v>
-      </c>
-      <c r="F11" t="str">
-        <v>A+</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Aditya Bose</v>
-      </c>
-      <c r="B12" t="str">
-        <v>Student</v>
-      </c>
-      <c r="C12" t="str">
-        <v>SA-2024-011</v>
-      </c>
-      <c r="D12" t="str">
-        <v>Grade 12-B</v>
-      </c>
-      <c r="E12" t="str">
-        <v>011</v>
-      </c>
-      <c r="F12" t="str">
-        <v>B+</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Kavya Menon</v>
-      </c>
-      <c r="B13" t="str">
-        <v>Student</v>
-      </c>
-      <c r="C13" t="str">
-        <v>SA-2024-012</v>
-      </c>
-      <c r="D13" t="str">
-        <v>Grade 12-B</v>
-      </c>
-      <c r="E13" t="str">
-        <v>012</v>
-      </c>
-      <c r="F13" t="str">
-        <v>O-</v>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" t="s">
+        <v>46</v>
+      </c>
+      <c r="F10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" t="s">
+        <v>49</v>
+      </c>
+      <c r="F11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12" t="s">
+        <v>53</v>
+      </c>
+      <c r="F12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>54</v>
+      </c>
+      <c r="B13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" t="s">
+        <v>52</v>
+      </c>
+      <c r="E13" t="s">
+        <v>56</v>
+      </c>
+      <c r="F13" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F13"/>
-  </ignoredErrors>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>